--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/CALIFORNIA_2015.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2015/CALIFORNIA_2015.xlsx
@@ -625,7 +625,7 @@
         <v>34</v>
       </c>
       <c r="D15">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="16">
@@ -1057,7 +1057,7 @@
         <v>34</v>
       </c>
       <c r="D39">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="40">
@@ -3649,7 +3649,7 @@
         <v>34</v>
       </c>
       <c r="D183">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="184">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Cuatro Cienegas</t>
+          <t>Cuatrocienegas</t>
         </is>
       </c>
       <c r="C209">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>General Simon Bolivar</t>
+          <t>Gral. Simon Bolivar</t>
         </is>
       </c>
       <c r="C266">
@@ -5575,7 +5575,7 @@
         <v>34</v>
       </c>
       <c r="D290">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="291">
@@ -6169,7 +6169,7 @@
         <v>333</v>
       </c>
       <c r="D323">
-        <v>0.0009176511437570787</v>
+        <v>0.0009176511437570788</v>
       </c>
     </row>
     <row r="324">
@@ -7771,7 +7771,7 @@
         <v>333</v>
       </c>
       <c r="D412">
-        <v>0.0009176511437570787</v>
+        <v>0.0009176511437570788</v>
       </c>
     </row>
     <row r="413">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C433">
@@ -10921,7 +10921,7 @@
         <v>34</v>
       </c>
       <c r="D587">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="588">
@@ -11209,7 +11209,7 @@
         <v>341</v>
       </c>
       <c r="D603">
-        <v>0.0009396968168803719</v>
+        <v>0.000939696816880372</v>
       </c>
     </row>
     <row r="604">
@@ -13441,7 +13441,7 @@
         <v>341</v>
       </c>
       <c r="D727">
-        <v>0.0009396968168803719</v>
+        <v>0.000939696816880372</v>
       </c>
     </row>
     <row r="728">
@@ -16519,7 +16519,7 @@
         <v>332</v>
       </c>
       <c r="D898">
-        <v>0.0009148954346166671</v>
+        <v>0.0009148954346166672</v>
       </c>
     </row>
     <row r="899">
@@ -18175,7 +18175,7 @@
         <v>336</v>
       </c>
       <c r="D990">
-        <v>0.0009259182711783137</v>
+        <v>0.0009259182711783136</v>
       </c>
     </row>
     <row r="991">
@@ -19957,7 +19957,7 @@
         <v>34</v>
       </c>
       <c r="D1089">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="1090">
@@ -21048,7 +21048,7 @@
       </c>
       <c r="B1150" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C1150">
@@ -21066,7 +21066,7 @@
       </c>
       <c r="B1151" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 26 -</t>
+          <t>San Juan Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1151">
@@ -22117,7 +22117,7 @@
         <v>34</v>
       </c>
       <c r="D1209">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="1210">
@@ -22866,7 +22866,7 @@
       </c>
       <c r="B1251" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C1251">
@@ -22884,7 +22884,7 @@
       </c>
       <c r="B1252" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 26 -</t>
+          <t>San Pedro Mixtepec -Dto. 26 -</t>
         </is>
       </c>
       <c r="C1252">
@@ -24763,7 +24763,7 @@
         <v>34</v>
       </c>
       <c r="D1356">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="1357">
@@ -26358,7 +26358,7 @@
       </c>
       <c r="B1445" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C1445">
@@ -29443,7 +29443,7 @@
         <v>34</v>
       </c>
       <c r="D1616">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="1617">
@@ -34987,7 +34987,7 @@
         <v>34</v>
       </c>
       <c r="D1924">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="1925">
@@ -35167,7 +35167,7 @@
         <v>350</v>
       </c>
       <c r="D1934">
-        <v>0.0009644981991440767</v>
+        <v>0.0009644981991440768</v>
       </c>
     </row>
     <row r="1935">
@@ -35473,7 +35473,7 @@
         <v>34</v>
       </c>
       <c r="D1951">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="1952">
@@ -36006,7 +36006,7 @@
       </c>
       <c r="B1981" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C1981">
@@ -36355,7 +36355,7 @@
         <v>34</v>
       </c>
       <c r="D2000">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="2001">
@@ -37687,7 +37687,7 @@
         <v>34</v>
       </c>
       <c r="D2074">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="2075">
@@ -38875,7 +38875,7 @@
         <v>34</v>
       </c>
       <c r="D2140">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="2141">
@@ -39613,7 +39613,7 @@
         <v>34</v>
       </c>
       <c r="D2181">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="2182">
@@ -41935,7 +41935,7 @@
         <v>34</v>
       </c>
       <c r="D2310">
-        <v>9.369411077399603E-05</v>
+        <v>9.369411077399604E-05</v>
       </c>
     </row>
     <row r="2311">
